--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -85,55 +85,67 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>QUIAHUA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>YEPEZ</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
   </si>
   <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>JACOBO</t>
-  </si>
-  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>MORALES</t>
   </si>
   <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
-    <t>JONATHAN MICHEL</t>
-  </si>
-  <si>
-    <t>DIEGO JOSUE</t>
-  </si>
-  <si>
     <t>YAEL</t>
   </si>
   <si>
+    <t>EMILIANO GERARDO</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
     <t>DIANA KELLY</t>
-  </si>
-  <si>
-    <t>AXEL</t>
   </si>
 </sst>
 </file>
@@ -703,16 +715,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.38</v>
+      </c>
+      <c r="H2">
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -726,16 +741,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81.81999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -749,16 +767,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>97.14</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -772,16 +793,19 @@
         <v>21</v>
       </c>
       <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
         <v>21</v>
       </c>
-      <c r="E5">
-        <v>21</v>
-      </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -795,16 +819,19 @@
         <v>23</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>95.65000000000001</v>
+      </c>
+      <c r="H6">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -860,16 +887,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>83.78</v>
+        <v>78.38</v>
       </c>
       <c r="H2">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -886,13 +913,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>69.7</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H3">
         <v>7.4</v>
@@ -912,16 +939,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G4">
-        <v>94.29000000000001</v>
+        <v>97.14</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -938,16 +965,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5">
-        <v>95.23999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -973,7 +1000,7 @@
         <v>95.65000000000001</v>
       </c>
       <c r="H6">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -983,7 +1010,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1015,22 +1042,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920271</v>
+        <v>24330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1038,22 +1065,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920371</v>
+        <v>24330051920038</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1061,16 +1088,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920385</v>
+        <v>24330051920271</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1090,10 +1117,10 @@
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1107,47 +1134,70 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920374</v>
+        <v>22330051920205</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>24330051920380</v>
+        <v>23330051920341</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
       </c>
       <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920374</v>
+      </c>
+      <c r="B8" t="s">
         <v>28</v>
       </c>
-      <c r="D7" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
+      <c r="C8" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
   <si>
     <t>Mat</t>
   </si>
@@ -85,12 +85,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
@@ -100,18 +94,9 @@
     <t>ANTONIO</t>
   </si>
   <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
     <t>NICIO</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -121,18 +106,9 @@
     <t>AGUILAR</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
-  </si>
-  <si>
     <t>CRISTHIAN GAEL</t>
   </si>
   <si>
@@ -140,9 +116,6 @@
   </si>
   <si>
     <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
   </si>
   <si>
     <t>DIANA KELLY</t>
@@ -1010,7 +983,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1042,22 +1015,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920040</v>
+        <v>24330051920271</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1065,22 +1038,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920038</v>
+        <v>24330051920381</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1088,22 +1061,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920271</v>
+        <v>22330051920205</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1111,93 +1084,24 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920381</v>
+        <v>24330051920374</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920205</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920341</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920374</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -91,6 +91,9 @@
     <t>YEPEZ</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>ANTONIO</t>
   </si>
   <si>
@@ -103,6 +106,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>AGUILAR</t>
   </si>
   <si>
@@ -113,6 +119,9 @@
   </si>
   <si>
     <t>YAEL</t>
+  </si>
+  <si>
+    <t>ANGEL GABRIEL</t>
   </si>
   <si>
     <t>EMILIANO GERARDO</t>
@@ -983,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1021,10 +1030,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1044,10 +1053,10 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1061,22 +1070,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920205</v>
+        <v>23330051920263</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1084,24 +1093,47 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920374</v>
+        <v>22330051920205</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920374</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
         <v>11</v>
       </c>
-      <c r="G5">
+      <c r="G6">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="51">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,21 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MOTA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>VILLARREAL</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
@@ -100,6 +115,18 @@
     <t>NICIO</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>DE URIARTE</t>
+  </si>
+  <si>
     <t>DOMINGUEZ</t>
   </si>
   <si>
@@ -113,6 +140,21 @@
   </si>
   <si>
     <t>MORALES</t>
+  </si>
+  <si>
+    <t>SARA ALY</t>
+  </si>
+  <si>
+    <t>DIANA CAMILA</t>
+  </si>
+  <si>
+    <t>DAMARIZ</t>
+  </si>
+  <si>
+    <t>RAFAEL</t>
+  </si>
+  <si>
+    <t>ANDY ARELY</t>
   </si>
   <si>
     <t>CRISTHIAN GAEL</t>
@@ -992,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,116 +1066,231 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920271</v>
+        <v>24330051920040</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920381</v>
+        <v>24330051920038</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920263</v>
+        <v>23330051920341</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920205</v>
+        <v>24330051920060</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>24330051920374</v>
+        <v>24330051920028</v>
       </c>
       <c r="B6" t="s">
         <v>26</v>
       </c>
       <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>24330051920271</v>
+      </c>
+      <c r="B7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>24330051920381</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>23330051920263</v>
+      </c>
+      <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920205</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>24330051920374</v>
+      </c>
+      <c r="B11" t="s">
         <v>31</v>
       </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
         <v>11</v>
       </c>
-      <c r="G6">
+      <c r="G11">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
   <si>
     <t>Mat</t>
   </si>
@@ -85,91 +85,31 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>MOTA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>VILLARREAL</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
   </si>
   <si>
     <t>SANTIAGO</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>YEPEZ</t>
-  </si>
-  <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>NICIO</t>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
   </si>
   <si>
     <t>FLORES</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>DE URIARTE</t>
-  </si>
-  <si>
-    <t>DOMINGUEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SARA ALY</t>
-  </si>
-  <si>
-    <t>DIANA CAMILA</t>
-  </si>
-  <si>
-    <t>DAMARIZ</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
+    <t>ANGEL GAEL</t>
+  </si>
+  <si>
+    <t>YOSHUA RAFAEL</t>
   </si>
   <si>
     <t>ANDY ARELY</t>
-  </si>
-  <si>
-    <t>CRISTHIAN GAEL</t>
-  </si>
-  <si>
-    <t>YAEL</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>EMILIANO GERARDO</t>
-  </si>
-  <si>
-    <t>DIANA KELLY</t>
   </si>
 </sst>
 </file>
@@ -582,7 +522,7 @@
         <v>83.78</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -608,7 +548,7 @@
         <v>69.7</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -671,10 +611,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -683,7 +623,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -742,16 +682,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>78.38</v>
+        <v>83.78</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -768,16 +708,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -840,10 +780,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -852,7 +792,7 @@
         <v>22</v>
       </c>
       <c r="G6">
-        <v>95.65000000000001</v>
+        <v>91.67</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -911,16 +851,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>78.38</v>
+        <v>94.59</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -937,16 +877,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>81.81999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -963,16 +903,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -998,7 +938,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1009,22 +949,22 @@
         <v>15</v>
       </c>
       <c r="C6">
+        <v>24</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>23</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>22</v>
-      </c>
       <c r="G6">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +974,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1066,16 +1006,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920040</v>
+        <v>24330051920375</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1089,22 +1029,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920038</v>
+        <v>24330051920259</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1112,186 +1052,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920341</v>
+        <v>24330051920028</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>24330051920060</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" t="s">
-        <v>44</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>24330051920028</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>24330051920271</v>
-      </c>
-      <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7">
         <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>24330051920381</v>
-      </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>47</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920263</v>
-      </c>
-      <c r="B9" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920205</v>
-      </c>
-      <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>24330051920374</v>
-      </c>
-      <c r="B11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,12 @@
     <t>REYES</t>
   </si>
   <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
     <t>RUIZ</t>
   </si>
   <si>
@@ -97,6 +103,12 @@
     <t>MORA</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
     <t>PELLICO</t>
   </si>
   <si>
@@ -104,6 +116,12 @@
   </si>
   <si>
     <t>ANGEL GAEL</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>NESTOR NOE</t>
   </si>
   <si>
     <t>YOSHUA RAFAEL</t>
@@ -974,7 +992,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1012,10 +1030,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1029,22 +1047,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>24330051920259</v>
+        <v>22330051920225</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G3">
         <v>4</v>
@@ -1052,16 +1070,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920028</v>
+        <v>24330051920009</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1070,6 +1088,52 @@
         <v>12</v>
       </c>
       <c r="G4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>24330051920259</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>24330051920028</v>
+      </c>
+      <c r="B6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
+++ b/docentes/Camacho Juárez Sergio Eduardo - Estadisticos 20241.xlsx
@@ -85,46 +85,46 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>VALDIVIA</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>SANTIAGO</t>
   </si>
   <si>
+    <t>TENORIO</t>
+  </si>
+  <si>
+    <t>PIEDRAS</t>
+  </si>
+  <si>
+    <t>PELLICO</t>
+  </si>
+  <si>
     <t>MORA</t>
   </si>
   <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PIEDRAS</t>
-  </si>
-  <si>
-    <t>PELLICO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>IKER YHAIR</t>
+  </si>
+  <si>
+    <t>NESTOR NOE</t>
+  </si>
+  <si>
+    <t>YOSHUA RAFAEL</t>
+  </si>
+  <si>
     <t>ANGEL GAEL</t>
-  </si>
-  <si>
-    <t>ANGELA</t>
-  </si>
-  <si>
-    <t>NESTOR NOE</t>
-  </si>
-  <si>
-    <t>YOSHUA RAFAEL</t>
   </si>
   <si>
     <t>ANDY ARELY</t>
@@ -632,16 +632,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -801,16 +801,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6">
-        <v>91.67</v>
+        <v>95.83</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -970,16 +970,16 @@
         <v>24</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>9</v>
@@ -1024,7 +1024,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>24330051920375</v>
+        <v>24330051920341</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
@@ -1042,12 +1042,12 @@
         <v>11</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920225</v>
+        <v>24330051920009</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
@@ -1059,18 +1059,18 @@
         <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G3">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>24330051920009</v>
+        <v>24330051920259</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -1088,12 +1088,12 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>24330051920259</v>
+        <v>24330051920375</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
@@ -1108,10 +1108,10 @@
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1134,7 +1134,7 @@
         <v>12</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
